--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1091,27 +1091,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128522630</v>
+        <v>136931186</v>
       </c>
       <c r="B5" t="n">
-        <v>99118</v>
+        <v>99355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1121,37 +1121,22 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Forsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488211</v>
+        <v>488262</v>
       </c>
       <c r="R5" t="n">
-        <v>7061410</v>
+        <v>7061337</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1175,17 +1160,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 130 plantor, 5 överblommade blomställningar och 3 avfröade vinterståndare inom ca 1 m2 yta nära ett igensatt dike.</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1196,61 +1176,74 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128522630</t>
+          <t>https://artportalen.se/Sighting/136931186</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128522990</v>
+        <v>128522630</v>
       </c>
       <c r="B6" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1262,13 +1255,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488248</v>
+        <v>488211</v>
       </c>
       <c r="R6" t="n">
-        <v>7061430</v>
+        <v>7061410</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1298,6 +1291,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minst 130 plantor, 5 överblommade blomställningar och 3 avfröade vinterståndare inom ca 1 m2 yta nära ett igensatt dike.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1327,6 +1325,118 @@
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128522630</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128522990</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>488248</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7061430</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128522990</t>
         </is>
@@ -1339,6 +1449,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -1094,7 +1094,7 @@
         <v>136931186</v>
       </c>
       <c r="B5" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -1094,7 +1094,7 @@
         <v>136931186</v>
       </c>
       <c r="B5" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -1094,7 +1094,7 @@
         <v>136931186</v>
       </c>
       <c r="B5" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -1094,7 +1094,7 @@
         <v>136931186</v>
       </c>
       <c r="B5" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -1094,7 +1094,7 @@
         <v>136931186</v>
       </c>
       <c r="B5" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128527000</v>
+        <v>137189704</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488539</v>
+        <v>488617</v>
       </c>
       <c r="R2" t="n">
-        <v>7061301</v>
+        <v>7061246</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,12 +766,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -777,14 +785,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,64 +804,54 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128527000</t>
+          <t>https://artportalen.se/Sighting/137189704</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128521444</v>
+        <v>128527000</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488479</v>
+        <v>488539</v>
       </c>
       <c r="R3" t="n">
-        <v>7061484</v>
+        <v>7061301</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,11 +883,6 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -921,12 +909,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -943,64 +931,57 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128521444</t>
+          <t>https://artportalen.se/Sighting/128527000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128521582</v>
+        <v>137189390</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>79485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488464</v>
+        <v>487944</v>
       </c>
       <c r="R4" t="n">
-        <v>7061484</v>
+        <v>7061164</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1024,17 +1005,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, högt upp på stammen av en gran vid hyggeskanten. Fyndplatsen finns i gammal flerskiktad granskog med bitvis minst medelhögt livsmiljövärde för tretåig hackspett.</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,12 +1019,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1063,12 +1040,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1085,58 +1062,57 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128521582</t>
+          <t>https://artportalen.se/Sighting/137189390</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136931186</v>
+        <v>137189391</v>
       </c>
       <c r="B5" t="n">
-        <v>99374</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219811</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Forsåsen, Jmt</t>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488262</v>
+        <v>487973</v>
       </c>
       <c r="R5" t="n">
-        <v>7061337</v>
+        <v>7061184</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1160,12 +1136,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,37 +1155,64 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Staffan Fridh</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136931186</t>
+          <t>https://artportalen.se/Sighting/137189391</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128522630</v>
+        <v>137189392</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,53 +1220,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488211</v>
+        <v>488000</v>
       </c>
       <c r="R6" t="n">
-        <v>7061410</v>
+        <v>7061210</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,17 +1277,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minst 130 plantor, 5 överblommade blomställningar och 3 avfröade vinterståndare inom ca 1 m2 yta nära ett igensatt dike.</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1304,12 +1291,38 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1326,59 +1339,57 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128522630</t>
+          <t>https://artportalen.se/Sighting/137189392</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128522990</v>
+        <v>137189393</v>
       </c>
       <c r="B7" t="n">
-        <v>97989</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488248</v>
+        <v>488009</v>
       </c>
       <c r="R7" t="n">
-        <v>7061430</v>
+        <v>7061258</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1402,12 +1413,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,12 +1427,38 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1437,6 +1474,4266 @@
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189393</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137189394</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79485</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>488002</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7061271</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en gran.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189394</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137189722</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79485</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>488233</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7061215</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189722</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137189723</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79485</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>488560</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7061248</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189723</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137189721</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79242</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>488030</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7061087</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Kolad ved.</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad ved.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189721</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128521444</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>488479</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7061484</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128521444</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128521582</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>488464</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7061484</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, högt upp på stammen av en gran vid hyggeskanten. Fyndplatsen finns i gammal flerskiktad granskog med bitvis minst medelhögt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128521582</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137189380</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>487906</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7061230</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, några meter upp på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189380</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137189381</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>487928</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7061172</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en klen gran vid en hyggeskant.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189381</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137189382</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>487943</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7061139</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en smal gran några meter in från en hyggeskant. Kring fyndplatsen finns stående död ved som indikerar medelhögt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189382</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137189383</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>487934</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7061150</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189383</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137189384</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>488006</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7061257</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189384</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137189385</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>488082</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7061309</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en tall nära vägen.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189385</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137189705</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>487955</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7061085</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189705</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137189706</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>487957</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7061080</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189706</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137189707</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>487960</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7061063</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189707</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137189708</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>487969</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7061032</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189708</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137189709</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>488316</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7061277</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189709</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137189710</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>488312</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7061270</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189710</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137189711</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>488313</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7061239</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189711</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137189712</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>488309</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7061168</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189712</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137189713</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>488439</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7061196</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en tall.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189713</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137189714</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>488742</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7061278</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189714</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137189715</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>488649</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7061274</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189715</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137189386</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>488008</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7061232</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 1 talltita med lockläte i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189386</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137189387</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>488481</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7061364</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Minst 1 talltita med lockläte i flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189387</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137189718</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>488400</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7061173</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189718</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137189716</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>488604</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7061271</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189716</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136931186</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99376</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Forsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>488262</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7061337</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136931186</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137189388</v>
+      </c>
+      <c r="B36" t="n">
+        <v>111353</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>488003</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7061205</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189388</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137189389</v>
+      </c>
+      <c r="B37" t="n">
+        <v>111353</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Nordöst om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>488477</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7061358</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137189389</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128522630</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>488211</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7061410</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 130 plantor, 5 överblommade blomställningar och 3 avfröade vinterståndare inom ca 1 m2 yta nära ett igensatt dike.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128522630</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128522990</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>488248</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7061430</v>
+      </c>
+      <c r="S39" t="n">
+        <v>8</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128522990</t>
         </is>
@@ -1450,6 +5747,38 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137189704</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137189390</v>
       </c>
       <c r="B4" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>137189391</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>137189392</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>137189393</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>137189394</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>137189722</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>137189723</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>137189721</v>
       </c>
       <c r="B11" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>136931186</v>
       </c>
       <c r="B35" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>137189388</v>
       </c>
       <c r="B36" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>137189389</v>
       </c>
       <c r="B37" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137189704</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137189390</v>
       </c>
       <c r="B4" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>137189391</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>137189392</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>137189393</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>137189394</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>137189722</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>137189723</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>137189721</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>137189380</v>
       </c>
       <c r="B14" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>137189381</v>
       </c>
       <c r="B15" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>137189382</v>
       </c>
       <c r="B16" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>137189383</v>
       </c>
       <c r="B17" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>137189384</v>
       </c>
       <c r="B18" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>137189385</v>
       </c>
       <c r="B19" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>137189705</v>
       </c>
       <c r="B20" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>137189706</v>
       </c>
       <c r="B21" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>137189707</v>
       </c>
       <c r="B22" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>137189708</v>
       </c>
       <c r="B23" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>137189709</v>
       </c>
       <c r="B24" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>137189710</v>
       </c>
       <c r="B25" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>137189711</v>
       </c>
       <c r="B26" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>137189712</v>
       </c>
       <c r="B27" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>137189713</v>
       </c>
       <c r="B28" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>137189714</v>
       </c>
       <c r="B29" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>137189715</v>
       </c>
       <c r="B30" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>137189386</v>
       </c>
       <c r="B31" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137189387</v>
       </c>
       <c r="B32" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>137189718</v>
       </c>
       <c r="B33" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>137189716</v>
       </c>
       <c r="B34" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>136931186</v>
       </c>
       <c r="B35" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>137189388</v>
       </c>
       <c r="B36" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>137189389</v>
       </c>
       <c r="B37" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137189704</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137189390</v>
       </c>
       <c r="B4" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>137189391</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>137189392</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>137189393</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>137189394</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>137189722</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>137189723</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>137189721</v>
       </c>
       <c r="B11" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>137189380</v>
       </c>
       <c r="B14" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>137189381</v>
       </c>
       <c r="B15" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>137189382</v>
       </c>
       <c r="B16" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>137189383</v>
       </c>
       <c r="B17" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>137189384</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>137189385</v>
       </c>
       <c r="B19" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>137189705</v>
       </c>
       <c r="B20" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>137189706</v>
       </c>
       <c r="B21" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>137189707</v>
       </c>
       <c r="B22" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>137189708</v>
       </c>
       <c r="B23" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>137189709</v>
       </c>
       <c r="B24" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>137189710</v>
       </c>
       <c r="B25" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>137189711</v>
       </c>
       <c r="B26" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>137189712</v>
       </c>
       <c r="B27" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>137189713</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>137189714</v>
       </c>
       <c r="B29" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>137189715</v>
       </c>
       <c r="B30" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>137189386</v>
       </c>
       <c r="B31" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137189387</v>
       </c>
       <c r="B32" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>137189718</v>
       </c>
       <c r="B33" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>137189716</v>
       </c>
       <c r="B34" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>136931186</v>
       </c>
       <c r="B35" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>137189388</v>
       </c>
       <c r="B36" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>137189389</v>
       </c>
       <c r="B37" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -710,11 +710,7 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -2315,11 +2311,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2455,11 +2447,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2595,11 +2583,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2735,11 +2719,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2875,11 +2855,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -3020,11 +2996,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3155,11 +3127,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3295,11 +3263,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3430,11 +3394,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3570,11 +3530,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3710,11 +3666,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3845,11 +3797,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3985,11 +3933,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -4125,11 +4069,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4265,11 +4205,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4405,11 +4341,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4540,11 +4472,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4679,11 +4607,7 @@
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4812,11 +4736,7 @@
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4940,11 +4860,7 @@
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5063,11 +4979,7 @@
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5291,11 +5203,7 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
@@ -5412,11 +5320,7 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137189704</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>136931186</v>
       </c>
       <c r="B35" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>137189388</v>
       </c>
       <c r="B36" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>137189389</v>
       </c>
       <c r="B37" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137189704</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>137189390</v>
       </c>
       <c r="B4" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>137189391</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>137189392</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137189393</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137189394</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>137189722</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>137189723</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>137189721</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137189380</v>
       </c>
       <c r="B14" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>137189381</v>
       </c>
       <c r="B15" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>137189382</v>
       </c>
       <c r="B16" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>137189383</v>
       </c>
       <c r="B17" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>137189384</v>
       </c>
       <c r="B18" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>137189385</v>
       </c>
       <c r="B19" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>137189705</v>
       </c>
       <c r="B20" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137189706</v>
       </c>
       <c r="B21" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>137189707</v>
       </c>
       <c r="B22" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>137189708</v>
       </c>
       <c r="B23" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>137189709</v>
       </c>
       <c r="B24" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>137189710</v>
       </c>
       <c r="B25" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>137189711</v>
       </c>
       <c r="B26" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>137189712</v>
       </c>
       <c r="B27" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>137189713</v>
       </c>
       <c r="B28" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>137189714</v>
       </c>
       <c r="B29" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>137189715</v>
       </c>
       <c r="B30" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>137189386</v>
       </c>
       <c r="B31" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>137189387</v>
       </c>
       <c r="B32" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137189718</v>
       </c>
       <c r="B33" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>137189716</v>
       </c>
       <c r="B34" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>136931186</v>
       </c>
       <c r="B35" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>137189388</v>
       </c>
       <c r="B36" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>137189389</v>
       </c>
       <c r="B37" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137189704</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>136931186</v>
       </c>
       <c r="B35" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>137189388</v>
       </c>
       <c r="B36" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>137189389</v>
       </c>
       <c r="B37" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137189704</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>137189390</v>
       </c>
       <c r="B4" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>137189391</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>137189392</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137189393</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137189394</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>137189722</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>137189723</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>137189721</v>
       </c>
       <c r="B11" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137189380</v>
       </c>
       <c r="B14" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>137189381</v>
       </c>
       <c r="B15" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>137189382</v>
       </c>
       <c r="B16" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>137189383</v>
       </c>
       <c r="B17" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>137189384</v>
       </c>
       <c r="B18" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>137189385</v>
       </c>
       <c r="B19" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>137189705</v>
       </c>
       <c r="B20" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137189706</v>
       </c>
       <c r="B21" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>137189707</v>
       </c>
       <c r="B22" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>137189708</v>
       </c>
       <c r="B23" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>137189709</v>
       </c>
       <c r="B24" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>137189710</v>
       </c>
       <c r="B25" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>137189711</v>
       </c>
       <c r="B26" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>137189712</v>
       </c>
       <c r="B27" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>137189713</v>
       </c>
       <c r="B28" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>137189714</v>
       </c>
       <c r="B29" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>137189715</v>
       </c>
       <c r="B30" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>137189386</v>
       </c>
       <c r="B31" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>137189387</v>
       </c>
       <c r="B32" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137189718</v>
       </c>
       <c r="B33" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>137189716</v>
       </c>
       <c r="B34" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>136931186</v>
       </c>
       <c r="B35" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>137189388</v>
       </c>
       <c r="B36" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>137189389</v>
       </c>
       <c r="B37" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137189704</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>136931186</v>
       </c>
       <c r="B35" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>137189388</v>
       </c>
       <c r="B36" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>137189389</v>
       </c>
       <c r="B37" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137189704</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>137189390</v>
       </c>
       <c r="B4" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>137189391</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>137189392</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137189393</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137189394</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>137189722</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>137189723</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>137189721</v>
       </c>
       <c r="B11" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137189380</v>
       </c>
       <c r="B14" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>137189381</v>
       </c>
       <c r="B15" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>137189382</v>
       </c>
       <c r="B16" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>137189383</v>
       </c>
       <c r="B17" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>137189384</v>
       </c>
       <c r="B18" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>137189385</v>
       </c>
       <c r="B19" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>137189705</v>
       </c>
       <c r="B20" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137189706</v>
       </c>
       <c r="B21" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>137189707</v>
       </c>
       <c r="B22" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>137189708</v>
       </c>
       <c r="B23" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>137189709</v>
       </c>
       <c r="B24" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>137189710</v>
       </c>
       <c r="B25" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>137189711</v>
       </c>
       <c r="B26" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>137189712</v>
       </c>
       <c r="B27" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>137189713</v>
       </c>
       <c r="B28" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>137189714</v>
       </c>
       <c r="B29" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>137189715</v>
       </c>
       <c r="B30" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>137189386</v>
       </c>
       <c r="B31" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>137189387</v>
       </c>
       <c r="B32" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137189718</v>
       </c>
       <c r="B33" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>137189716</v>
       </c>
       <c r="B34" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>136931186</v>
       </c>
       <c r="B35" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>137189388</v>
       </c>
       <c r="B36" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>137189389</v>
       </c>
       <c r="B37" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -5176,7 +5176,7 @@
         <v>137189388</v>
       </c>
       <c r="B36" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>137189389</v>
       </c>
       <c r="B37" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137189704</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>137189390</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>137189391</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>137189392</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137189393</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137189394</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>137189722</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>137189723</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>137189721</v>
       </c>
       <c r="B11" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>136931186</v>
       </c>
       <c r="B35" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>137189388</v>
       </c>
       <c r="B36" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>137189389</v>
       </c>
       <c r="B37" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137189704</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>137189390</v>
       </c>
       <c r="B4" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>137189391</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>137189392</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137189393</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137189394</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>137189722</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>137189723</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>137189721</v>
       </c>
       <c r="B11" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>136931186</v>
       </c>
       <c r="B35" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>137189388</v>
       </c>
       <c r="B36" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>137189389</v>
       </c>
       <c r="B37" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137189704</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>137189390</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>137189391</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>137189392</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137189393</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137189394</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>137189722</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>137189723</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>137189721</v>
       </c>
       <c r="B11" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>136931186</v>
       </c>
       <c r="B35" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>137189388</v>
       </c>
       <c r="B36" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>137189389</v>
       </c>
       <c r="B37" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -5066,7 +5066,7 @@
         <v>136931186</v>
       </c>
       <c r="B35" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 37569-2026 artfynd.xlsx
+++ b/artfynd/A 37569-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137189704</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>137189390</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>137189391</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>137189392</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137189393</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137189394</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>137189722</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>137189723</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>137189721</v>
       </c>
       <c r="B11" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137189380</v>
       </c>
       <c r="B14" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>137189381</v>
       </c>
       <c r="B15" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>137189382</v>
       </c>
       <c r="B16" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>137189383</v>
       </c>
       <c r="B17" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>137189384</v>
       </c>
       <c r="B18" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>137189385</v>
       </c>
       <c r="B19" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>137189705</v>
       </c>
       <c r="B20" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>137189706</v>
       </c>
       <c r="B21" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>137189707</v>
       </c>
       <c r="B22" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>137189708</v>
       </c>
       <c r="B23" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>137189709</v>
       </c>
       <c r="B24" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>137189710</v>
       </c>
       <c r="B25" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>137189711</v>
       </c>
       <c r="B26" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>137189712</v>
       </c>
       <c r="B27" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>137189713</v>
       </c>
       <c r="B28" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>137189714</v>
       </c>
       <c r="B29" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>137189715</v>
       </c>
       <c r="B30" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>137189386</v>
       </c>
       <c r="B31" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>137189387</v>
       </c>
       <c r="B32" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137189718</v>
       </c>
       <c r="B33" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>137189716</v>
       </c>
       <c r="B34" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>136931186</v>
       </c>
       <c r="B35" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>137189388</v>
       </c>
       <c r="B36" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>137189389</v>
       </c>
       <c r="B37" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
